--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/pre LAM_HRM-2031-0240/Panel 7/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/pre LAM_HRM-2031-0240/Panel 7/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.34923</v>
+        <v>17.66353</v>
       </c>
       <c r="D2" t="n">
-        <v>17.56423</v>
+        <v>17.42891</v>
       </c>
       <c r="E2" t="n">
-        <v>17.50307</v>
+        <v>17.50634</v>
       </c>
       <c r="F2" t="n">
-        <v>44.0756</v>
+        <v>44.62378</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05389</v>
+        <v>0.05268</v>
       </c>
       <c r="H2" t="n">
-        <v>1.92335</v>
+        <v>1.92757</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.40886</v>
+        <v>17.55168</v>
       </c>
       <c r="D3" t="n">
-        <v>17.68907</v>
+        <v>17.12609</v>
       </c>
       <c r="E3" t="n">
-        <v>17.5226</v>
+        <v>17.30048</v>
       </c>
       <c r="F3" t="n">
-        <v>44.23557</v>
+        <v>44.95154</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05312</v>
+        <v>0.05251</v>
       </c>
       <c r="H3" t="n">
-        <v>1.92684</v>
+        <v>1.92307</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.55561</v>
+        <v>17.66972</v>
       </c>
       <c r="D4" t="n">
-        <v>17.88736</v>
+        <v>17.03062</v>
       </c>
       <c r="E4" t="n">
-        <v>17.96172</v>
+        <v>17.44669</v>
       </c>
       <c r="F4" t="n">
-        <v>43.78832</v>
+        <v>44.20142</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05364</v>
+        <v>0.05252</v>
       </c>
       <c r="H4" t="n">
-        <v>1.90979</v>
+        <v>1.86759</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.33233</v>
+        <v>17.49901</v>
       </c>
       <c r="D6" t="n">
-        <v>17.1166</v>
+        <v>16.77897</v>
       </c>
       <c r="E6" t="n">
-        <v>17.33903</v>
+        <v>17.37465</v>
       </c>
       <c r="F6" t="n">
-        <v>23.22228</v>
+        <v>22.73157</v>
       </c>
       <c r="G6" t="n">
-        <v>36.26716</v>
+        <v>36.252</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.52054</v>
+        <v>17.33224</v>
       </c>
       <c r="D7" t="n">
-        <v>16.7218</v>
+        <v>16.77382</v>
       </c>
       <c r="E7" t="n">
-        <v>17.11113</v>
+        <v>16.90916</v>
       </c>
       <c r="F7" t="n">
-        <v>22.91158</v>
+        <v>22.55274</v>
       </c>
       <c r="G7" t="n">
-        <v>35.65945</v>
+        <v>35.64113</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.55959</v>
+        <v>17.53735</v>
       </c>
       <c r="D8" t="n">
-        <v>16.68673</v>
+        <v>16.848</v>
       </c>
       <c r="E8" t="n">
-        <v>17.32073</v>
+        <v>17.1926</v>
       </c>
       <c r="F8" t="n">
-        <v>23.21459</v>
+        <v>22.58996</v>
       </c>
       <c r="G8" t="n">
-        <v>36.36475</v>
+        <v>36.54988</v>
       </c>
     </row>
   </sheetData>
